--- a/docs/sources/master_song_links.xlsx
+++ b/docs/sources/master_song_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.83203125" customWidth="1" min="1" max="1"/>
@@ -469,36 +469,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Angel From Montgomery</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kingsofewing.com/docs/music/angel_from_montgomery.pdf</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>https://tabs.ultimate-guitar.com/tab/john-prine/angel-from-montgomery-official-3010223</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All These Things That I've Done</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.kingsofewing.com/docs/music/all%20these%20things%20that%20ive%20done%20official.pdf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/the-killers/all-these-things-that-ive-done-official-2141163</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Back On 74</t>
+          <t>Angel From Montgomery</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -513,19 +513,19 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/back%20on%2074%20official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/angel_from_montgomery.pdf</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/jungle/back-on-74-official-4968148</t>
+          <t>https://tabs.ultimate-guitar.com/tab/john-prine/angel-from-montgomery-official-3010223</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Back On 74</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -540,19 +540,19 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/black.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/back%20on%2074%20official.pdf</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/pearl-jam/black-official-2451097</t>
+          <t>https://tabs.ultimate-guitar.com/tab/jungle/back-on-74-official-4968148</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Bohemian Like You</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -567,19 +567,19 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/Bohemian%20Like%20You.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/black.pdf</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-dandy-warhols/bohemian-like-you-official-2829043</t>
+          <t>https://tabs.ultimate-guitar.com/tab/pearl-jam/black-official-2451097</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Come Together</t>
+          <t>Bohemian Like You</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -594,19 +594,19 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/come%20together%20official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/Bohemian%20Like%20You.pdf</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-beatles/come-together-official-1950291</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-dandy-warhols/bohemian-like-you-official-2829043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Crossroads</t>
+          <t>Come Together</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -621,19 +621,19 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/Crossroads.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/come%20together%20official.pdf</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/cream/crossroads-official-1983079</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-beatles/come-together-official-1950291</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Dedicated Follower Of Fashion</t>
+          <t>Crossroads</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -648,19 +648,19 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/dedicated%20follower%20of%20fashion.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/Crossroads.pdf</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-kinks/dedicated-follower-of-fashion-official-4884518</t>
+          <t>https://tabs.ultimate-guitar.com/tab/cream/crossroads-official-1983079</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Don't Let Me Down</t>
+          <t>Dedicated Follower Of Fashion</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -675,19 +675,19 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/dont%20let%20me%20down.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/dedicated%20follower%20of%20fashion.pdf</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-beatles/dont-let-me-down-official-1962071</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-kinks/dedicated-follower-of-fashion-official-4884518</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Don't Look Back In Anger</t>
+          <t>Don't Let Me Down</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -702,19 +702,19 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/dont_look_back_in_anger_official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/dont%20let%20me%20down.pdf</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/oasis/dont-look-back-in-anger-official-1910905</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-beatles/dont-let-me-down-official-1962071</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Down By The River</t>
+          <t>Don't Look Back In Anger</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -729,19 +729,19 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/down%20by%20the%20river.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/dont_look_back_in_anger_official.pdf</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/neil-young/down-by-the-river-official-2701248</t>
+          <t>https://tabs.ultimate-guitar.com/tab/oasis/dont-look-back-in-anger-official-1910905</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>End Of The World</t>
+          <t>Down By The River</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -756,19 +756,19 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/end_of_the_world.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/down%20by%20the%20river.pdf</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/r-e-m-/its-the-end-of-the-world-as-we-know-it-and-i-feel-fine-official-2789386</t>
+          <t>https://tabs.ultimate-guitar.com/tab/neil-young/down-by-the-river-official-2701248</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Follow Your Arrow</t>
+          <t>End Of The World</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -783,19 +783,19 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/follow_your_arrow_official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/end_of_the_world.pdf</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/kacey-musgraves/follow-your-arrow-official-4171309</t>
+          <t>https://tabs.ultimate-guitar.com/tab/r-e-m-/its-the-end-of-the-world-as-we-know-it-and-i-feel-fine-official-2789386</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>For What It's Worth</t>
+          <t>Follow Your Arrow</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -810,19 +810,19 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/for_what_its_worth.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/follow_your_arrow_official.pdf</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/buffalo-springfield/for-what-its-worth-official-1956147</t>
+          <t>https://tabs.ultimate-guitar.com/tab/kacey-musgraves/follow-your-arrow-official-4171309</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Fortunate Son</t>
+          <t>For What It's Worth</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -837,19 +837,19 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/fortunate%20son.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/for_what_its_worth.pdf</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/creedence-clearwater-revival/fortunate-son-official-1945887</t>
+          <t>https://tabs.ultimate-guitar.com/tab/buffalo-springfield/for-what-its-worth-official-1956147</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Found Out About You</t>
+          <t>Fortunate Son</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -864,19 +864,19 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/found%20out%20about%20you.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/fortunate%20son.pdf</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/gin-blossoms/found-out-about-you-official-3430250</t>
+          <t>https://tabs.ultimate-guitar.com/tab/creedence-clearwater-revival/fortunate-son-official-1945887</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>From The Start</t>
+          <t>Found Out About You</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/from%20the%20start%20official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/found%20out%20about%20you.pdf</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/laufey/from-the-start-official-4776938</t>
+          <t>https://tabs.ultimate-guitar.com/tab/gin-blossoms/found-out-about-you-official-3430250</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Guess Again</t>
+          <t>From The Start</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -918,19 +918,19 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/guess_again.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/from%20the%20start%20official.pdf</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/jeff-tweedy/guess-again-chords-3344825</t>
+          <t>https://tabs.ultimate-guitar.com/tab/laufey/from-the-start-official-4776938</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Head Over Heels</t>
+          <t>Guess Again</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -945,19 +945,19 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/head%20over%20heels%20official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/guess_again.pdf</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/tears-for-fears/head-over-heels-official-2717880</t>
+          <t>https://tabs.ultimate-guitar.com/tab/jeff-tweedy/guess-again-chords-3344825</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Heroes</t>
+          <t>Head Over Heels</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -972,19 +972,19 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/heroes.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/head%20over%20heels%20official.pdf</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/david-bowie/heroes-official-2457982</t>
+          <t>https://tabs.ultimate-guitar.com/tab/tears-for-fears/head-over-heels-official-2717880</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>I've Got A Feeling</t>
+          <t>Heroes</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/ive_got_a_feeling_official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/heroes.pdf</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-beatles/ive-got-a-feeling-official-2631297</t>
+          <t>https://tabs.ultimate-guitar.com/tab/david-bowie/heroes-official-2457982</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Just Like Heaven</t>
+          <t>I've Got A Feeling</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1026,19 +1026,19 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/just%20like%20heaven.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/ive_got_a_feeling_official.pdf</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-cure/just-like-heaven-official-1961213</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-beatles/ive-got-a-feeling-official-2631297</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Just What I Needed</t>
+          <t>Just Like Heaven</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1053,19 +1053,19 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/just_what_i_needed.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/just%20like%20heaven.pdf</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-cars/just-what-i-needed-official-2212159</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-cure/just-like-heaven-official-1961213</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kings Of Ewing</t>
+          <t>Just What I Needed</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1073,17 +1073,26 @@
           <t>PDF</t>
         </is>
       </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/kings%20of%20ewing.pdf</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="n"/>
+          <t>https://www.kingsofewing.com/docs/music/just_what_i_needed.pdf</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/the-cars/just-what-i-needed-official-2212159</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Laid</t>
+          <t>Kings Of Ewing</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1091,26 +1100,17 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/laid.pdf</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>https://tabs.ultimate-guitar.com/tab/james/laid-official-2685951</t>
-        </is>
-      </c>
+          <t>https://www.kingsofewing.com/docs/music/kings%20of%20ewing.pdf</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Let Me Roll It</t>
+          <t>Laid</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1125,19 +1125,19 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/let%20me%20roll%20it%20official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/laid.pdf</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/wings/let-me-roll-it-official-3333080</t>
+          <t>https://tabs.ultimate-guitar.com/tab/james/laid-official-2685951</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Little By Little</t>
+          <t>Let Me Roll It</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1152,19 +1152,19 @@
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/little_by_little.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/let%20me%20roll%20it%20official.pdf</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/oasis/little-by-little-official-2497398</t>
+          <t>https://tabs.ultimate-guitar.com/tab/wings/let-me-roll-it-official-3333080</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Message In A Bottle</t>
+          <t>Little By Little</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1179,19 +1179,19 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/message_in_a_bottle.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/little_by_little.pdf</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-police/message-in-a-bottle-official-1957169</t>
+          <t>https://tabs.ultimate-guitar.com/tab/oasis/little-by-little-official-2497398</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Midnight Rider</t>
+          <t>Message In A Bottle</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1206,19 +1206,19 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/midnight%20rider.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/message_in_a_bottle.pdf</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-allman-brothers-band/midnight-rider-official-2611482</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-police/message-in-a-bottle-official-1957169</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>No One To Depend On</t>
+          <t>Midnight Rider</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1233,19 +1233,19 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/no%20one%20to%20depend%20on.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/midnight%20rider.pdf</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/santana/no-one-to-depend-on-chords-3337193</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-allman-brothers-band/midnight-rider-official-2611482</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Octopus's Garden</t>
+          <t>No One To Depend On</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1260,19 +1260,19 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/octopus_garden.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/no%20one%20to%20depend%20on.pdf</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-beatles/octopuss-garden-official-1957271</t>
+          <t>https://tabs.ultimate-guitar.com/tab/santana/no-one-to-depend-on-chords-3337193</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Octopus's Garden</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1287,19 +1287,19 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/ohio.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/octopus_garden.pdf</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/neil-young/ohio-official-2548995</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-beatles/octopuss-garden-official-1957271</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Pink Pony Club</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1314,19 +1314,19 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/pink_pony_club.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/ohio.pdf</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/chappell-roan/pink-pony-club-official-5236500</t>
+          <t>https://tabs.ultimate-guitar.com/tab/neil-young/ohio-official-2548995</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Riders On The Storm</t>
+          <t>Pink Pony Club</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1341,19 +1341,19 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/riders%20on%20the%20storm.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/pink_pony_club.pdf</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-doors/riders-on-the-storm-official-2212149</t>
+          <t>https://tabs.ultimate-guitar.com/tab/chappell-roan/pink-pony-club-official-5236500</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Rockin' In The Free World</t>
+          <t>Riders On The Storm</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1368,19 +1368,19 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/rockin%20in%20the%20free%20world.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/riders%20on%20the%20storm.pdf</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/neil-young/rockin-in-the-free-world-official-2518044</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-doors/riders-on-the-storm-official-2212149</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Seven Nation Army</t>
+          <t>Rockin' In The Free World</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1395,19 +1395,19 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/seven%20nation%20army.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/rockin%20in%20the%20free%20world.pdf</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-white-stripes/seven-nation-army-official-1911521</t>
+          <t>https://tabs.ultimate-guitar.com/tab/neil-young/rockin-in-the-free-world-official-2518044</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>She Bangs The Drums</t>
+          <t>Seven Nation Army</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1422,19 +1422,19 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/she%20bangs%20the%20drums%20official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/seven%20nation%20army.pdf</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-stone-roses/she-bangs-the-drums-official-2984609</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-white-stripes/seven-nation-army-official-1911521</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Smooth Operator</t>
+          <t>She Bangs The Drums</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1449,19 +1449,19 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/smooth_operator.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/she%20bangs%20the%20drums%20official.pdf</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/sade/smooth-operator-official-1979485</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-stone-roses/she-bangs-the-drums-official-2984609</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Starlight</t>
+          <t>Smooth Operator</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/starlight.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/smooth_operator.pdf</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/muse/starlight-official-1940709</t>
+          <t>https://tabs.ultimate-guitar.com/tab/sade/smooth-operator-official-1979485</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Sympathy For The Devil</t>
+          <t>Starlight</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/sympathy%20for%20the%20devil.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/starlight.pdf</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-rolling-stones/sympathy-for-the-devil-official-2383129</t>
+          <t>https://tabs.ultimate-guitar.com/tab/muse/starlight-official-1940709</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Teach Your Children</t>
+          <t>Sympathy For The Devil</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1530,19 +1530,19 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/Teach%20Your%20Children.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/sympathy%20for%20the%20devil.pdf</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/crosby-stills-nash-young/teach-your-children-official-2815919</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-rolling-stones/sympathy-for-the-devil-official-2383129</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>That's What I Love</t>
+          <t>Teach Your Children</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1557,19 +1557,19 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/thats_what_i_love_chords.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/Teach%20Your%20Children.pdf</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/leon-bridges/thats-what-i-love-chords-5492289</t>
+          <t>https://tabs.ultimate-guitar.com/tab/crosby-stills-nash-young/teach-your-children-official-2815919</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>The Seeker</t>
+          <t>That's What I Love</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/the_seeker_official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/thats_what_i_love_chords.pdf</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-who/the-seeker-official-2938316</t>
+          <t>https://tabs.ultimate-guitar.com/tab/leon-bridges/thats-what-i-love-chords-5492289</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Voodoo Child</t>
+          <t>The Seeker</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1611,19 +1611,19 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/voodoo_child.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/the_seeker_official.pdf</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/jimi-hendrix/voodoo-child-slight-return-official-2420407</t>
+          <t>https://tabs.ultimate-guitar.com/tab/the-who/the-seeker-official-2938316</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Walk On</t>
+          <t>Voodoo Child</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1638,19 +1638,19 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/walk_on_chords.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/voodoo_child.pdf</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/neil-young/walk-on-chords-88633</t>
+          <t>https://tabs.ultimate-guitar.com/tab/jimi-hendrix/voodoo-child-slight-return-official-2420407</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>War Pigs</t>
+          <t>Walk On</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1665,19 +1665,19 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/war_pigs_official.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/walk_on_chords.pdf</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/black-sabbath/war-pigs-official-2003333</t>
+          <t>https://tabs.ultimate-guitar.com/tab/neil-young/walk-on-chords-88633</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Whipping Post</t>
+          <t>War Pigs</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1692,73 +1692,100 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>https://www.kingsofewing.com/docs/music/whipping_post.pdf</t>
+          <t>https://www.kingsofewing.com/docs/music/war_pigs_official.pdf</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>https://tabs.ultimate-guitar.com/tab/the-allman-brothers-band/whipping-post-official-2639163</t>
+          <t>https://tabs.ultimate-guitar.com/tab/black-sabbath/war-pigs-official-2003333</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Who's That Lady</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n"/>
-      <c r="E49" s="1" t="n"/>
+          <t>Whipping Post</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>https://www.kingsofewing.com/docs/music/whipping_post.pdf</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/the-allman-brothers-band/whipping-post-official-2639163</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Won't Back Down</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>https://www.kingsofewing.com/docs/music/won%27t%20back%20down.pdf</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>https://tabs.ultimate-guitar.com/tab/tom-petty/i-wont-back-down-official-2175865</t>
-        </is>
-      </c>
+          <t>Who's That Lady</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n"/>
+      <c r="E50" s="1" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
+          <t>Won't Back Down</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>https://www.kingsofewing.com/docs/music/won%27t%20back%20down.pdf</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>https://tabs.ultimate-guitar.com/tab/tom-petty/i-wont-back-down-official-2175865</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
           <t>Sunny Afternoon</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>https://www.kingsofewing.com/docs/music/sunny_afternoon.pdf</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>https://tabs.ultimate-guitar.com/tab/the-kinks/sunny-afternoon-official-2139793</t>
         </is>
